--- a/Analysis/failure_inclusive_metrics.xlsx
+++ b/Analysis/failure_inclusive_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,47 +464,67 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>kendall_tau_headline</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>spearman_rho_conditional</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>spearman_rho_inclusive</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>spearman_rho_delta</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>spearman_rho_headline</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>top1_accuracy_conditional</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>top1_accuracy_inclusive</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>top1_accuracy_delta</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>top1_accuracy_headline</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>top2_accuracy_conditional</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>top2_accuracy_inclusive</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>top2_accuracy_delta</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>top2_accuracy_headline</t>
         </is>
       </c>
     </row>
@@ -528,46 +548,58 @@
         <v>65</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0293</v>
+        <v>0.0421</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0287</v>
+        <v>0.0421</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0052</v>
+        <v>0.0421</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0046</v>
+        <v>0.0369</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0005</v>
+        <v>0.0369</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3171</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3169</v>
+        <v>0.0369</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0001</v>
+        <v>0.3538</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6308</v>
+        <v>0.3538</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6308</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0.3538</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -590,46 +622,58 @@
         <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1021</v>
+        <v>-0.1105</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1019</v>
+        <v>-0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.103</v>
+        <v>-0.1105</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1029</v>
+        <v>-0.12</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001</v>
+        <v>-0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1978</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1981</v>
+        <v>-0.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0002</v>
+        <v>0.26</v>
       </c>
       <c r="P3" t="n">
-        <v>0.639</v>
+        <v>0.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.639</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="4">
@@ -652,46 +696,58 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.144</v>
+        <v>0.1248</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1429</v>
+        <v>0.1248</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0011</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1452</v>
+        <v>0.1248</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1441</v>
+        <v>0.1313</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0011</v>
+        <v>0.1313</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3668</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3665</v>
+        <v>0.1313</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0003</v>
+        <v>0.3908</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7221</v>
+        <v>0.3908</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7217</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0004</v>
+        <v>0.3908</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7292</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7292</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7292</v>
       </c>
     </row>
     <row r="5">
@@ -714,46 +770,58 @@
         <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5577</v>
+        <v>0.4889</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5522</v>
+        <v>0.4889</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0054</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5891</v>
+        <v>0.4889</v>
       </c>
       <c r="K5" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5266999999999999</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.5833</v>
       </c>
-      <c r="L5" t="n">
-        <v>-0.0057</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.6194</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.6167</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.0028</v>
-      </c>
       <c r="P5" t="n">
-        <v>0.9192</v>
+        <v>0.5833</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9167</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0025</v>
+        <v>0.5833</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="6">
@@ -782,40 +850,52 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0215</v>
+        <v>0.1097</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0215</v>
+        <v>0.1097</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.1097</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.0785</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0785</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2492</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2492</v>
+        <v>0.0785</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.3631</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5754</v>
+        <v>0.3631</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5754</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.3631</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.6892</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6892</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.6892</v>
       </c>
     </row>
     <row r="7">
@@ -844,40 +924,52 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0324</v>
+        <v>-0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0324</v>
+        <v>-0.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0371</v>
+        <v>-0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0371</v>
+        <v>-0.1771</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.1771</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2543</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2543</v>
+        <v>-0.1771</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1914</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6143</v>
+        <v>0.1914</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6143</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.1914</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5229</v>
       </c>
     </row>
     <row r="8">
@@ -906,40 +998,52 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1761</v>
+        <v>0.1788</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1761</v>
+        <v>0.1788</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1733</v>
+        <v>0.1788</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1733</v>
+        <v>0.1836</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.1836</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3621</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3621</v>
+        <v>0.1836</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.3979</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6974</v>
+        <v>0.3979</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6974</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3979</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7026</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.7026</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7026</v>
       </c>
     </row>
     <row r="9">
@@ -968,40 +1072,52 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6333</v>
+        <v>0.6956</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6333</v>
+        <v>0.6956</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6883</v>
+        <v>0.6956</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6883</v>
+        <v>0.7183</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.7183</v>
       </c>
       <c r="M9" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.61</v>
+        <v>0.7183</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.6767</v>
       </c>
       <c r="P9" t="n">
+        <v>0.6767</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6767</v>
+      </c>
+      <c r="S9" t="n">
         <v>0.9267</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>0.9267</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.9267</v>
       </c>
     </row>
     <row r="10">
@@ -1030,40 +1146,52 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1467</v>
+        <v>-0.1138</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1467</v>
+        <v>-0.1138</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1662</v>
+        <v>-0.1138</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1662</v>
+        <v>-0.1215</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.1215</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2677</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2677</v>
+        <v>-0.1215</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.3385</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5569</v>
+        <v>0.3385</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5569</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.3385</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.6092</v>
       </c>
     </row>
     <row r="11">
@@ -1092,40 +1220,52 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1352</v>
+        <v>0.0914</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1352</v>
+        <v>0.0914</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1429</v>
+        <v>0.0914</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1429</v>
+        <v>0.1114</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.1114</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3971</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3971</v>
+        <v>0.1114</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.3457</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7571</v>
+        <v>0.3457</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7571</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.3457</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.7171</v>
       </c>
     </row>
     <row r="12">
@@ -1154,40 +1294,52 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0407</v>
+        <v>0.0325</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0407</v>
+        <v>0.0325</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0385</v>
+        <v>0.0325</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0385</v>
+        <v>0.0379</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.0379</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3333</v>
+        <v>0.0379</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.3405</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6646</v>
+        <v>0.3405</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6646</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.3405</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.6656</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.6656</v>
       </c>
     </row>
     <row r="13">
@@ -1216,40 +1368,52 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1333</v>
+        <v>0.1222</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1333</v>
+        <v>0.1222</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1383</v>
+        <v>0.1222</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1383</v>
+        <v>0.125</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.125</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.3367</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6733</v>
+        <v>0.3367</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6733</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.3367</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.6667</v>
       </c>
     </row>
     <row r="14">
@@ -1272,46 +1436,58 @@
         <v>65</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0309</v>
+        <v>-0.0544</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0308</v>
+        <v>-0.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.037</v>
+        <v>-0.0544</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0369</v>
+        <v>-0.0646</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001</v>
+        <v>-0.0646</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2315</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2318</v>
+        <v>-0.0646</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0003</v>
+        <v>0.2462</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.2462</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6758999999999999</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0.2462</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6831</v>
       </c>
     </row>
     <row r="15">
@@ -1334,46 +1510,58 @@
         <v>70</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0027</v>
+        <v>-0.0147</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0029</v>
+        <v>-0.0143</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0128</v>
+        <v>-0.0143</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0129</v>
+        <v>-0.0221</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0001</v>
+        <v>-0.0214</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3265</v>
+        <v>0.0007</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3267</v>
+        <v>-0.0214</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0001</v>
+        <v>0.3038</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6735</v>
+        <v>0.3048</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6733</v>
+        <v>0.0009</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.0001</v>
+        <v>0.2943</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.6371</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.6381</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6171</v>
       </c>
     </row>
     <row r="16">
@@ -1396,46 +1584,58 @@
         <v>195</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01</v>
+        <v>0.0055</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0055</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0078</v>
+        <v>0.0055</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0077</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0001</v>
+        <v>-0.0005</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3001</v>
+        <v>0.0001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3002</v>
+        <v>-0.0005</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.3112</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6773</v>
+        <v>0.3115</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6773</v>
+        <v>0.0003</v>
       </c>
       <c r="R16" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6722</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6721</v>
+      </c>
+      <c r="U16" t="n">
         <v>-0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.6646</v>
       </c>
     </row>
     <row r="17">
@@ -1464,40 +1664,52 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0689</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0689</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3433</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3433</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6833</v>
+        <v>0.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6833</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="18">
@@ -1520,46 +1732,58 @@
         <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4174</v>
+        <v>0.2879</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4174</v>
+        <v>0.2872</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4662</v>
+        <v>0.2872</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4662</v>
+        <v>0.3131</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.3123</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7015</v>
+        <v>-0.0008</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7015</v>
+        <v>0.3123</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.6019</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9015</v>
+        <v>0.601</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9015</v>
+        <v>-0.0008</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.8425</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.8421</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="19">
@@ -1588,40 +1812,52 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0419</v>
+        <v>0.0305</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0419</v>
+        <v>0.0305</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0371</v>
+        <v>0.0305</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0371</v>
+        <v>0.0243</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0243</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3286</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3286</v>
+        <v>0.0243</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.2971</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6629</v>
+        <v>0.2971</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6629</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.2971</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.7171</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.7171</v>
       </c>
     </row>
     <row r="20">
@@ -1644,46 +1880,58 @@
         <v>195</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3067</v>
+        <v>0.2533</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3067</v>
+        <v>0.253</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3308</v>
+        <v>0.253</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3308</v>
+        <v>0.2695</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.2692</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5354</v>
+        <v>-0.0003</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5354</v>
+        <v>0.2692</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.4836</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8113</v>
+        <v>0.4834</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8113</v>
+        <v>-0.0002</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4831</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.8173</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.8171</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.8164</v>
       </c>
     </row>
     <row r="21">
@@ -1712,40 +1960,52 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4956</v>
+        <v>0.4756</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4956</v>
+        <v>0.4756</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.4756</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.5083</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.5083</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5967</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5967</v>
+        <v>0.5083</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.5733</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8867</v>
+        <v>0.5733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8867</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.5733</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.9067</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.9067</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9067</v>
       </c>
     </row>
     <row r="22">
@@ -1768,46 +2028,58 @@
         <v>65</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3441</v>
+        <v>0.3026</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3364</v>
+        <v>0.3026</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0077</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3352</v>
+        <v>0.3026</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3277</v>
+        <v>0.32</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0075</v>
+        <v>0.32</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5629999999999999</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5579</v>
+        <v>0.32</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0051</v>
+        <v>0.5446</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7611</v>
+        <v>0.5446</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.759</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.0021</v>
+        <v>0.5446</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.7907999999999999</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.7907999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1830,46 +2102,58 @@
         <v>70</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1162</v>
+        <v>-0.1181</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1152</v>
+        <v>-0.1181</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0936</v>
+        <v>-0.1181</v>
       </c>
       <c r="K23" t="n">
         <v>-0.0929</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0008</v>
+        <v>-0.0929</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1528</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1543</v>
+        <v>-0.0929</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0014</v>
+        <v>0.1514</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6657</v>
+        <v>0.1514</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6657</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.1514</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.5857</v>
       </c>
     </row>
     <row r="24">
@@ -1892,46 +2176,58 @@
         <v>195</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3099</v>
+        <v>0.2985</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3067</v>
+        <v>0.2985</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0032</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.328</v>
+        <v>0.2985</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3246</v>
+        <v>0.321</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0034</v>
+        <v>0.321</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4871</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4855</v>
+        <v>0.321</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0016</v>
+        <v>0.4749</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7958</v>
+        <v>0.4749</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.7945</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.0013</v>
+        <v>0.4749</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.7713</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.7713</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.7713</v>
       </c>
     </row>
     <row r="25">
@@ -1960,40 +2256,52 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7667</v>
+        <v>0.78</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7667</v>
+        <v>0.78</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8083</v>
+        <v>0.78</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8083</v>
+        <v>0.805</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.805</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7933</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7933</v>
+        <v>0.805</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9833</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9833</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.7766999999999999</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.9667</v>
       </c>
     </row>
     <row r="26">
@@ -2022,40 +2330,52 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0482</v>
+        <v>-0.0728</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0482</v>
+        <v>-0.0728</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0769</v>
+        <v>-0.0728</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0769</v>
+        <v>-0.0815</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>-0.0815</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3046</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3046</v>
+        <v>-0.0815</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>0.3262</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5938</v>
+        <v>0.3262</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5938</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.3262</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6123</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.6123</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.6123</v>
       </c>
     </row>
     <row r="27">
@@ -2084,40 +2404,52 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2648</v>
+        <v>0.2019</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2648</v>
+        <v>0.2019</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3014</v>
+        <v>0.2019</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3014</v>
+        <v>0.2171</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.2171</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4686</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.4686</v>
+        <v>0.2171</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>0.4029</v>
       </c>
       <c r="P27" t="n">
-        <v>0.7743</v>
+        <v>0.4029</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.7743</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.4029</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.7629</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.7629</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.7629</v>
       </c>
     </row>
     <row r="28">
@@ -2146,40 +2478,52 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2725</v>
+        <v>0.2342</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2725</v>
+        <v>0.2342</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2908</v>
+        <v>0.2342</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2908</v>
+        <v>0.2508</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.2508</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4738</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4738</v>
+        <v>0.2508</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>0.4646</v>
       </c>
       <c r="P28" t="n">
-        <v>0.7651</v>
+        <v>0.4646</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.7651</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>0.4646</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.7631</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.7631</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.7631</v>
       </c>
     </row>
     <row r="29">
@@ -2208,40 +2552,52 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6289</v>
+        <v>0.6044</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6289</v>
+        <v>0.6044</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6767</v>
+        <v>0.6044</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6767</v>
+        <v>0.65</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6633</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6633</v>
+        <v>0.65</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>0.6867</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6867</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.6867</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.9267</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.9267</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.9267</v>
       </c>
     </row>
     <row r="30">
@@ -2270,40 +2626,52 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2308</v>
+        <v>0.1487</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2308</v>
+        <v>0.1487</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2415</v>
+        <v>0.1487</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2415</v>
+        <v>0.1692</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.1692</v>
       </c>
       <c r="M30" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.52</v>
+        <v>0.1692</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>0.4738</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8092</v>
+        <v>0.4738</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8092</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>0.4738</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.7477</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.7477</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.7477</v>
       </c>
     </row>
     <row r="31">
@@ -2332,40 +2700,52 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.16</v>
+        <v>0.059</v>
       </c>
       <c r="H31" t="n">
-        <v>0.16</v>
+        <v>0.059</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1829</v>
+        <v>0.059</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1829</v>
+        <v>0.0614</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.0614</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4114</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4114</v>
+        <v>0.0614</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>0.3543</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7714</v>
+        <v>0.3543</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.7714</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>0.3543</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.7457</v>
       </c>
     </row>
     <row r="32">
@@ -2394,40 +2774,52 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2082</v>
+        <v>0.1474</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2082</v>
+        <v>0.1474</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2241</v>
+        <v>0.1474</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2241</v>
+        <v>0.159</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4656</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.4656</v>
+        <v>0.159</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="P32" t="n">
-        <v>0.7805</v>
+        <v>0.439</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.7805</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.439</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.7395</v>
       </c>
     </row>
     <row r="33">
@@ -2456,40 +2848,52 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.24</v>
+        <v>0.2489</v>
       </c>
       <c r="H33" t="n">
-        <v>0.24</v>
+        <v>0.2489</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2533</v>
+        <v>0.2489</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2533</v>
+        <v>0.2617</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.2617</v>
       </c>
       <c r="M33" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.47</v>
+        <v>0.2617</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.7233000000000001</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.7233000000000001</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.7233000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2518,40 +2922,52 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9754</v>
+        <v>0.9467</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9754</v>
+        <v>0.9467</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9815</v>
+        <v>0.9467</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9815</v>
+        <v>0.96</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9846</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.9846</v>
+        <v>0.96</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>0.9692</v>
       </c>
       <c r="P34" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="S34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2574,46 +2990,58 @@
         <v>70</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9198</v>
+        <v>0.795</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9171</v>
+        <v>0.7905</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0026</v>
+        <v>-0.0046</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9327</v>
+        <v>0.7905</v>
       </c>
       <c r="K35" t="n">
-        <v>0.93</v>
+        <v>0.8176</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.0027</v>
+        <v>0.8129</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9198</v>
+        <v>-0.0047</v>
       </c>
       <c r="N35" t="n">
-        <v>0.9181</v>
+        <v>0.8129</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.0017</v>
+        <v>0.8477</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9885</v>
+        <v>0.8448</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9876</v>
+        <v>-0.003</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.0009</v>
+        <v>0.8429</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.9454</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.9438</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2636,46 +3064,58 @@
         <v>195</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8973</v>
+        <v>0.8582</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8964</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0009</v>
+        <v>-0.0018</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9102</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9092</v>
+        <v>0.8762</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.0009</v>
+        <v>0.8744</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9076</v>
+        <v>-0.0018</v>
       </c>
       <c r="N36" t="n">
-        <v>0.907</v>
+        <v>0.8744</v>
       </c>
       <c r="O36" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.8862</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.9671</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.9665</v>
+      </c>
+      <c r="U36" t="n">
         <v>-0.0005999999999999999</v>
       </c>
-      <c r="P36" t="n">
-        <v>0.9774</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="R36" t="n">
-        <v>-0.0003</v>
+      <c r="V36" t="n">
+        <v>0.9651</v>
       </c>
     </row>
     <row r="37">
@@ -2704,40 +3144,52 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7867</v>
+        <v>0.8356</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7867</v>
+        <v>0.8356</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8067</v>
+        <v>0.8356</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8067</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.8467</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8467</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>0.8467</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.9567</v>
       </c>
     </row>
     <row r="38">
@@ -2766,40 +3218,52 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.959</v>
+        <v>0.9446</v>
       </c>
       <c r="H38" t="n">
-        <v>0.959</v>
+        <v>0.9446</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9692</v>
+        <v>0.9446</v>
       </c>
       <c r="K38" t="n">
-        <v>0.9692</v>
+        <v>0.9585</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.9585</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9692</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9692</v>
+        <v>0.9585</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>0.9538</v>
       </c>
       <c r="P38" t="n">
+        <v>0.9538</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.9538</v>
+      </c>
+      <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2828,40 +3292,52 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9771</v>
+        <v>0.8724</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9771</v>
+        <v>0.8724</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9829</v>
+        <v>0.8724</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9829</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9657</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0.9657</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>0.8829</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0.8829</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>0.8829</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.9714</v>
       </c>
     </row>
     <row r="40">
@@ -2890,40 +3366,52 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9234</v>
+        <v>0.8913</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9234</v>
+        <v>0.8913</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9349</v>
+        <v>0.8913</v>
       </c>
       <c r="K40" t="n">
-        <v>0.9349</v>
+        <v>0.9077</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.9077</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9313</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.9313</v>
+        <v>0.9077</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.9015</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9846</v>
+        <v>0.9015</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9846</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>0.9015</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.9795</v>
       </c>
     </row>
     <row r="41">
@@ -2952,40 +3440,52 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8222</v>
+        <v>0.8556</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8222</v>
+        <v>0.8556</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8417</v>
+        <v>0.8556</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8417</v>
+        <v>0.875</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="M41" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0.85</v>
+        <v>0.875</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>0.8667</v>
       </c>
       <c r="P41" t="n">
-        <v>0.95</v>
+        <v>0.8667</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.8667</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.9667</v>
       </c>
     </row>
     <row r="42">
@@ -3014,40 +3514,52 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9487</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9487</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.9754</v>
+        <v>0.9487</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9754</v>
+        <v>0.9615</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.9615</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9877</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.9877</v>
+        <v>0.9615</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>0.9631</v>
       </c>
       <c r="P42" t="n">
+        <v>0.9631</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.9631</v>
+      </c>
+      <c r="S42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="T42" t="n">
         <v>1</v>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3070,46 +3582,58 @@
         <v>70</v>
       </c>
       <c r="E43" t="n">
-        <v>23.4</v>
+        <v>16.4</v>
       </c>
       <c r="F43" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9429</v>
+        <v>0.8589</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6276</v>
+        <v>0.6571</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3152</v>
+        <v>-0.2018</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9571</v>
+        <v>0.6571</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6371</v>
+        <v>0.885</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.32</v>
+        <v>0.6771</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9399</v>
+        <v>-0.2078</v>
       </c>
       <c r="N43" t="n">
-        <v>0.7371</v>
+        <v>0.6771</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.2027</v>
+        <v>0.8922</v>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>0.761</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.8885999999999999</v>
+        <v>-0.1313</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.1114</v>
+        <v>0.6829</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-0.0757</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.7571</v>
       </c>
     </row>
     <row r="44">
@@ -3132,46 +3656,58 @@
         <v>195</v>
       </c>
       <c r="E44" t="n">
-        <v>23.4</v>
+        <v>17</v>
       </c>
       <c r="F44" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8974</v>
+        <v>0.8819</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7897</v>
+        <v>0.8048</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1077</v>
+        <v>-0.0771</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9114</v>
+        <v>0.8048</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8021</v>
+        <v>0.8979</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.1093</v>
+        <v>0.8195</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9173</v>
+        <v>-0.0784</v>
       </c>
       <c r="N44" t="n">
-        <v>0.8472</v>
+        <v>0.8195</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.0701</v>
+        <v>0.9035</v>
       </c>
       <c r="P44" t="n">
-        <v>0.9813</v>
+        <v>0.8537</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9436</v>
+        <v>-0.0499</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.0377</v>
+        <v>0.8246</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.9515</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.8933</v>
       </c>
     </row>
     <row r="45">
@@ -3194,46 +3730,58 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7867</v>
+        <v>0.8294</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7867</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>-0.0083</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8067</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8067</v>
+        <v>0.8401</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8233</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>0.8233</v>
+        <v>0.8317</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>0.8485</v>
       </c>
       <c r="P45" t="n">
-        <v>0.9467</v>
+        <v>0.8433</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9467</v>
+        <v>-0.0052</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>0.84</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.9462</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="U45" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.9367</v>
       </c>
     </row>
     <row r="46">
@@ -3262,40 +3810,52 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9056</v>
+        <v>0.9077</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9056</v>
+        <v>0.9077</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9092</v>
+        <v>0.9077</v>
       </c>
       <c r="K46" t="n">
-        <v>0.9092</v>
+        <v>0.9185</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.9185</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9292</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.9292</v>
+        <v>0.9185</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>0.9385</v>
       </c>
       <c r="P46" t="n">
-        <v>0.9815</v>
+        <v>0.9385</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9815</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.9385</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.9877</v>
       </c>
     </row>
     <row r="47">
@@ -3318,46 +3878,58 @@
         <v>70</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8813</v>
+        <v>0.7543</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8762</v>
+        <v>0.7543</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0051</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8966</v>
+        <v>0.7543</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8914</v>
+        <v>0.7829</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.0052</v>
+        <v>0.7829</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8737</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.7829</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.0032</v>
+        <v>0.7743</v>
       </c>
       <c r="P47" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.7743</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9695</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.0018</v>
+        <v>0.7743</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.9371</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.9371</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.9371</v>
       </c>
     </row>
     <row r="48">
@@ -3380,46 +3952,58 @@
         <v>195</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8801</v>
+        <v>0.8359</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8783</v>
+        <v>0.8359</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0018</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8895</v>
+        <v>0.8359</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8877</v>
+        <v>0.8518</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.0018</v>
+        <v>0.8518</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8972</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0.8961</v>
+        <v>0.8518</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.0012</v>
+        <v>0.8646</v>
       </c>
       <c r="P48" t="n">
-        <v>0.9692</v>
+        <v>0.8646</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9685</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.8646</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="49">
@@ -3448,40 +4032,52 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8511</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8511</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.86</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="K49" t="n">
         <v>0.86</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O49" t="n">
         <v>0.89</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>0.89</v>
       </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0.9533</v>
-      </c>
       <c r="Q49" t="n">
-        <v>0.9533</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.9567</v>
       </c>
     </row>
   </sheetData>
